--- a/artfynd/A 20379-2025 artfynd.xlsx
+++ b/artfynd/A 20379-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63902122</v>
+        <v>73777798</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sundellsberget 4, Vb</t>
+          <t>Månberget norr, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>808285.3296683428</v>
+        <v>808381</v>
       </c>
       <c r="R2" t="n">
-        <v>7158419.515670121</v>
+        <v>7158350</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-08-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-08-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +754,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -797,12 +775,7 @@
         <v>63901931</v>
       </c>
       <c r="B3" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,230 +873,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>73777797</v>
-      </c>
-      <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Månberget norr, Vb</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>808314.9471637558</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7158466.893352608</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Lövånger</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2018-09-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2018-09-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>73777798</v>
-      </c>
-      <c r="B5" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>185</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Bryoria nadvornikiana</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Månberget norr, Vb</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>808381.2359716056</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7158350.040753596</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Lövånger</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2018-09-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2018-09-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20379-2025 artfynd.xlsx
+++ b/artfynd/A 20379-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73777798</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -873,8 +883,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63901931</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>